--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/116.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/116.xlsx
@@ -426,13 +426,13 @@
         <v>6.250432309009072</v>
       </c>
       <c r="E2">
-        <v>-19.7359069274564</v>
+        <v>-19.60996553682908</v>
       </c>
       <c r="F2">
-        <v>-2.884560998093614</v>
+        <v>-1.98751945249982</v>
       </c>
       <c r="G2">
-        <v>-11.99846762792306</v>
+        <v>-12.81095495635316</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.228951092545212</v>
       </c>
       <c r="E3">
-        <v>-20.18587874722856</v>
+        <v>-20.98380945280211</v>
       </c>
       <c r="F3">
-        <v>-2.669328780926426</v>
+        <v>-2.200872104030056</v>
       </c>
       <c r="G3">
-        <v>-11.56556745102581</v>
+        <v>-12.04542771639763</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>6.172912060148492</v>
       </c>
       <c r="E4">
-        <v>-19.62001874912611</v>
+        <v>-20.39137184074863</v>
       </c>
       <c r="F4">
-        <v>-3.087571482599897</v>
+        <v>-2.102838135378345</v>
       </c>
       <c r="G4">
-        <v>-11.43789957284935</v>
+        <v>-12.13668952527872</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>6.083552738358287</v>
       </c>
       <c r="E5">
-        <v>-20.88868885627099</v>
+        <v>-20.65666796201399</v>
       </c>
       <c r="F5">
-        <v>-2.733085734817696</v>
+        <v>-1.884827573942168</v>
       </c>
       <c r="G5">
-        <v>-11.88243300677161</v>
+        <v>-11.74976620483086</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>5.971581000736226</v>
       </c>
       <c r="E6">
-        <v>-21.15951424429971</v>
+        <v>-20.30992270724667</v>
       </c>
       <c r="F6">
-        <v>-2.685845598570845</v>
+        <v>-1.638149701797309</v>
       </c>
       <c r="G6">
-        <v>-11.8580276650561</v>
+        <v>-11.51751157197775</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.85069897526389</v>
       </c>
       <c r="E7">
-        <v>-22.15482301797158</v>
+        <v>-21.03424306782553</v>
       </c>
       <c r="F7">
-        <v>-2.636771456894197</v>
+        <v>-2.149809880586688</v>
       </c>
       <c r="G7">
-        <v>-11.26557574589367</v>
+        <v>-11.43855837141167</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.740581692149338</v>
       </c>
       <c r="E8">
-        <v>-21.43172081690078</v>
+        <v>-22.13335352270121</v>
       </c>
       <c r="F8">
-        <v>-2.428634206531988</v>
+        <v>-2.120616556577228</v>
       </c>
       <c r="G8">
-        <v>-11.19353496441359</v>
+        <v>-11.18669537732946</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.660658403161807</v>
       </c>
       <c r="E9">
-        <v>-23.14324851115178</v>
+        <v>-21.69867888812696</v>
       </c>
       <c r="F9">
-        <v>-2.47032676628229</v>
+        <v>-2.031215832997494</v>
       </c>
       <c r="G9">
-        <v>-10.89296722435762</v>
+        <v>-11.47137249879692</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.633264698788996</v>
       </c>
       <c r="E10">
-        <v>-22.92498059245607</v>
+        <v>-23.08396625791736</v>
       </c>
       <c r="F10">
-        <v>-2.609125523193167</v>
+        <v>-2.196822215797769</v>
       </c>
       <c r="G10">
-        <v>-10.69856867974608</v>
+        <v>-10.60452270206646</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.678932811691383</v>
       </c>
       <c r="E11">
-        <v>-23.92815985395326</v>
+        <v>-24.48246318638815</v>
       </c>
       <c r="F11">
-        <v>-2.428651602247446</v>
+        <v>-1.59338638408483</v>
       </c>
       <c r="G11">
-        <v>-10.12905884117079</v>
+        <v>-9.945624823385316</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.809043547526862</v>
       </c>
       <c r="E12">
-        <v>-24.52321492398317</v>
+        <v>-24.37924114985731</v>
       </c>
       <c r="F12">
-        <v>-2.3098347238269</v>
+        <v>-1.958594519528867</v>
       </c>
       <c r="G12">
-        <v>-10.15084554136474</v>
+        <v>-9.691696048886598</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.02735114678585</v>
       </c>
       <c r="E13">
-        <v>-24.525474632513</v>
+        <v>-25.22737451827988</v>
       </c>
       <c r="F13">
-        <v>-2.274148656114297</v>
+        <v>-2.010405587104365</v>
       </c>
       <c r="G13">
-        <v>-10.10055835462321</v>
+        <v>-8.553292133206336</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.329358241333681</v>
       </c>
       <c r="E14">
-        <v>-25.83279526531335</v>
+        <v>-25.67025927623004</v>
       </c>
       <c r="F14">
-        <v>-2.145874307055988</v>
+        <v>-1.978390015353567</v>
       </c>
       <c r="G14">
-        <v>-9.069998770430244</v>
+        <v>-9.220449823007963</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.696191704616799</v>
       </c>
       <c r="E15">
-        <v>-26.72845949692043</v>
+        <v>-26.79936181445852</v>
       </c>
       <c r="F15">
-        <v>-1.962061237109583</v>
+        <v>-1.783936566118203</v>
       </c>
       <c r="G15">
-        <v>-8.532862756683494</v>
+        <v>-7.881450021466642</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.105276799436615</v>
       </c>
       <c r="E16">
-        <v>-27.18897360418245</v>
+        <v>-27.1197468220272</v>
       </c>
       <c r="F16">
-        <v>-1.817719045539172</v>
+        <v>-1.652122603147731</v>
       </c>
       <c r="G16">
-        <v>-8.345201172244368</v>
+        <v>-7.752759184718553</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.532658334380029</v>
       </c>
       <c r="E17">
-        <v>-28.00114636051011</v>
+        <v>-28.09681943087017</v>
       </c>
       <c r="F17">
-        <v>-1.592980484057458</v>
+        <v>-1.396449489375872</v>
       </c>
       <c r="G17">
-        <v>-7.497777656738347</v>
+        <v>-7.197411859960272</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.949878480106305</v>
       </c>
       <c r="E18">
-        <v>-28.35632363387971</v>
+        <v>-28.90074583602986</v>
       </c>
       <c r="F18">
-        <v>-1.612179555352142</v>
+        <v>-1.387442650605233</v>
       </c>
       <c r="G18">
-        <v>-7.283413211979458</v>
+        <v>-6.790095578990502</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.33552149961144</v>
       </c>
       <c r="E19">
-        <v>-29.08752727495023</v>
+        <v>-29.94466324970006</v>
       </c>
       <c r="F19">
-        <v>-1.385209372087286</v>
+        <v>-1.071931589124749</v>
       </c>
       <c r="G19">
-        <v>-7.346174534312962</v>
+        <v>-5.467347245501464</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.673321740315462</v>
       </c>
       <c r="E20">
-        <v>-30.46592683577498</v>
+        <v>-29.88289939270944</v>
       </c>
       <c r="F20">
-        <v>-1.212092182045828</v>
+        <v>-0.6522988869493812</v>
       </c>
       <c r="G20">
-        <v>-6.852217966034926</v>
+        <v>-5.714562233646539</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.945928727492872</v>
       </c>
       <c r="E21">
-        <v>-31.43579917094575</v>
+        <v>-30.49850920626016</v>
       </c>
       <c r="F21">
-        <v>-1.141366173194807</v>
+        <v>-0.7754472985191669</v>
       </c>
       <c r="G21">
-        <v>-6.979104555464112</v>
+        <v>-5.702475431882661</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>9.144691299764903</v>
       </c>
       <c r="E22">
-        <v>-31.63818573129656</v>
+        <v>-30.95840744105714</v>
       </c>
       <c r="F22">
-        <v>-1.150541998915617</v>
+        <v>-1.009818116160634</v>
       </c>
       <c r="G22">
-        <v>-6.568394965316589</v>
+        <v>-4.893722398820866</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.26691905929664</v>
       </c>
       <c r="E23">
-        <v>-31.92143272352832</v>
+        <v>-31.80755065918343</v>
       </c>
       <c r="F23">
-        <v>-1.061192634114856</v>
+        <v>-0.609174079959639</v>
       </c>
       <c r="G23">
-        <v>-6.46909515186615</v>
+        <v>-5.199613496103985</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>9.308551597422644</v>
       </c>
       <c r="E24">
-        <v>-32.5633484425896</v>
+        <v>-32.61989776176038</v>
       </c>
       <c r="F24">
-        <v>-0.978466895066881</v>
+        <v>-0.4068221475385814</v>
       </c>
       <c r="G24">
-        <v>-6.427911965357616</v>
+        <v>-5.884022438710753</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>9.271985627595569</v>
       </c>
       <c r="E25">
-        <v>-32.24127431421607</v>
+        <v>-33.22240443576992</v>
       </c>
       <c r="F25">
-        <v>-0.8202263552122998</v>
+        <v>-0.2737913128533975</v>
       </c>
       <c r="G25">
-        <v>-6.240561572199182</v>
+        <v>-5.906971140388981</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>9.165168335493146</v>
       </c>
       <c r="E26">
-        <v>-33.10614265833399</v>
+        <v>-33.48244752718637</v>
       </c>
       <c r="F26">
-        <v>-0.8066204206213179</v>
+        <v>-0.7056730838139618</v>
       </c>
       <c r="G26">
-        <v>-6.046828447241031</v>
+        <v>-4.596594315580199</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.992653522050867</v>
       </c>
       <c r="E27">
-        <v>-33.10518488608137</v>
+        <v>-32.97724870265367</v>
       </c>
       <c r="F27">
-        <v>-0.6686715686657134</v>
+        <v>-0.6702777730597417</v>
       </c>
       <c r="G27">
-        <v>-6.060683080322882</v>
+        <v>-5.448348024651587</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.761670109798798</v>
       </c>
       <c r="E28">
-        <v>-32.94840911593582</v>
+        <v>-33.28335996015016</v>
       </c>
       <c r="F28">
-        <v>-0.6698859552782176</v>
+        <v>-0.3407731010437656</v>
       </c>
       <c r="G28">
-        <v>-5.796607483746297</v>
+        <v>-4.677550396197536</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.48475818104532</v>
       </c>
       <c r="E29">
-        <v>-33.18549284413339</v>
+        <v>-32.897740020264</v>
       </c>
       <c r="F29">
-        <v>-0.6651203576099119</v>
+        <v>-0.5636983662807518</v>
       </c>
       <c r="G29">
-        <v>-6.619443577532151</v>
+        <v>-5.950786210601235</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.1691043289212</v>
       </c>
       <c r="E30">
-        <v>-32.83721696515148</v>
+        <v>-33.29257993322977</v>
       </c>
       <c r="F30">
-        <v>-0.7726838648634278</v>
+        <v>-0.6658957094989323</v>
       </c>
       <c r="G30">
-        <v>-6.340437420573454</v>
+        <v>-5.42262177526591</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>7.822272765310929</v>
       </c>
       <c r="E31">
-        <v>-32.22270757078462</v>
+        <v>-33.27786465694185</v>
       </c>
       <c r="F31">
-        <v>-0.8159395539028124</v>
+        <v>-0.3198021518744933</v>
       </c>
       <c r="G31">
-        <v>-6.67004857664545</v>
+        <v>-5.55780459181651</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>7.457657713927105</v>
       </c>
       <c r="E32">
-        <v>-31.66160699886423</v>
+        <v>-33.41119198867568</v>
       </c>
       <c r="F32">
-        <v>-0.7489461685688051</v>
+        <v>-0.4374021585803279</v>
       </c>
       <c r="G32">
-        <v>-6.788102630575861</v>
+        <v>-6.10297861013261</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>7.083087461459461</v>
       </c>
       <c r="E33">
-        <v>-32.37552092617346</v>
+        <v>-32.02260788980769</v>
       </c>
       <c r="F33">
-        <v>-0.7275734612091751</v>
+        <v>-0.5345042139038888</v>
       </c>
       <c r="G33">
-        <v>-6.646215959308237</v>
+        <v>-6.040306672528668</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.704354842426681</v>
       </c>
       <c r="E34">
-        <v>-31.33492061971388</v>
+        <v>-31.01100113818223</v>
       </c>
       <c r="F34">
-        <v>-0.7043452108672742</v>
+        <v>-0.3370893512035162</v>
       </c>
       <c r="G34">
-        <v>-7.209700605002046</v>
+        <v>-6.147002244713838</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.332121605841705</v>
       </c>
       <c r="E35">
-        <v>-30.74216601447987</v>
+        <v>-32.18111127278716</v>
       </c>
       <c r="F35">
-        <v>-0.6721291742049986</v>
+        <v>-0.2366100419787417</v>
       </c>
       <c r="G35">
-        <v>-7.311698513066991</v>
+        <v>-5.871021926378035</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.971317277164758</v>
       </c>
       <c r="E36">
-        <v>-31.26604026582021</v>
+        <v>-30.90298118344026</v>
       </c>
       <c r="F36">
-        <v>-0.7323241482642303</v>
+        <v>-0.321914488751632</v>
       </c>
       <c r="G36">
-        <v>-7.28263854432327</v>
+        <v>-6.444633530876475</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.623542294361215</v>
       </c>
       <c r="E37">
-        <v>-29.45123392911328</v>
+        <v>-31.90938245419391</v>
       </c>
       <c r="F37">
-        <v>-0.6783228772757305</v>
+        <v>-0.2898442447522492</v>
       </c>
       <c r="G37">
-        <v>-6.975055758269583</v>
+        <v>-6.463503640450321</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.294186487380851</v>
       </c>
       <c r="E38">
-        <v>-30.55494531358076</v>
+        <v>-30.59166897354596</v>
       </c>
       <c r="F38">
-        <v>-0.4408879286113082</v>
+        <v>-0.0002163511396384231</v>
       </c>
       <c r="G38">
-        <v>-7.331714071397426</v>
+        <v>-5.449020065396058</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.984651613183953</v>
       </c>
       <c r="E39">
-        <v>-29.42567069333998</v>
+        <v>-28.82175566391407</v>
       </c>
       <c r="F39">
-        <v>-0.502727211965097</v>
+        <v>-0.01337248223090017</v>
       </c>
       <c r="G39">
-        <v>-7.687253420132993</v>
+        <v>-6.308388029207769</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>4.691619734834053</v>
       </c>
       <c r="E40">
-        <v>-29.00331577230359</v>
+        <v>-28.72171261613661</v>
       </c>
       <c r="F40">
-        <v>-0.6934770305425447</v>
+        <v>-0.04369818447998727</v>
       </c>
       <c r="G40">
-        <v>-7.052618529709168</v>
+        <v>-5.743059409648586</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.414472592721637</v>
       </c>
       <c r="E41">
-        <v>-29.06502075913211</v>
+        <v>-28.24999506417961</v>
       </c>
       <c r="F41">
-        <v>-0.3347690941082748</v>
+        <v>-0.3793104093568042</v>
       </c>
       <c r="G41">
-        <v>-7.571897460817089</v>
+        <v>-6.567885141303542</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>4.150450940269217</v>
       </c>
       <c r="E42">
-        <v>-27.22710335532703</v>
+        <v>-27.8750917580326</v>
       </c>
       <c r="F42">
-        <v>-0.1694153633658542</v>
+        <v>-0.08310942040297935</v>
       </c>
       <c r="G42">
-        <v>-7.518256691444278</v>
+        <v>-6.470114799892245</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.891824057729224</v>
       </c>
       <c r="E43">
-        <v>-26.93817312821565</v>
+        <v>-27.06985662388469</v>
       </c>
       <c r="F43">
-        <v>-0.1097016707676491</v>
+        <v>0.2484653417525928</v>
       </c>
       <c r="G43">
-        <v>-7.677692564615579</v>
+        <v>-6.968550536284916</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.633339773929408</v>
       </c>
       <c r="E44">
-        <v>-26.87833840115229</v>
+        <v>-26.35499624550786</v>
       </c>
       <c r="F44">
-        <v>-0.3051301084361084</v>
+        <v>0.1568818700664822</v>
       </c>
       <c r="G44">
-        <v>-8.202265058040794</v>
+        <v>-6.302574711240809</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.371318570546423</v>
       </c>
       <c r="E45">
-        <v>-26.25219535705973</v>
+        <v>-25.44432012256535</v>
       </c>
       <c r="F45">
-        <v>-0.3138221675936836</v>
+        <v>0.4963551154077476</v>
       </c>
       <c r="G45">
-        <v>-7.550203455898245</v>
+        <v>-6.816884513494284</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.097703160176426</v>
       </c>
       <c r="E46">
-        <v>-25.84752186278629</v>
+        <v>-25.61448206187757</v>
       </c>
       <c r="F46">
-        <v>-0.09009918454780158</v>
+        <v>0.3228759288112668</v>
       </c>
       <c r="G46">
-        <v>-8.796709925617868</v>
+        <v>-6.79741850572337</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.80788581659458</v>
       </c>
       <c r="E47">
-        <v>-24.59577919148208</v>
+        <v>-24.76826876643425</v>
       </c>
       <c r="F47">
-        <v>-0.1879575393101184</v>
+        <v>0.2591670202293596</v>
       </c>
       <c r="G47">
-        <v>-8.055948876841626</v>
+        <v>-6.712599018461703</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.502100896646579</v>
       </c>
       <c r="E48">
-        <v>-24.34750107553755</v>
+        <v>-24.27410809729523</v>
       </c>
       <c r="F48">
-        <v>-0.1196876398083971</v>
+        <v>0.5547881520012248</v>
       </c>
       <c r="G48">
-        <v>-8.205211443570747</v>
+        <v>-7.627756295701212</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.177121232114047</v>
       </c>
       <c r="E49">
-        <v>-23.44871672533918</v>
+        <v>-24.23651723455756</v>
       </c>
       <c r="F49">
-        <v>-0.1666933480802551</v>
+        <v>0.1801970989856771</v>
       </c>
       <c r="G49">
-        <v>-7.975870090792196</v>
+        <v>-6.666205033274356</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.833322130169681</v>
       </c>
       <c r="E50">
-        <v>-23.10690297876621</v>
+        <v>-24.20039812587238</v>
       </c>
       <c r="F50">
-        <v>0.09804376181303613</v>
+        <v>-0.02491578198891128</v>
       </c>
       <c r="G50">
-        <v>-8.096218352781321</v>
+        <v>-7.033563029585123</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.477146598459238</v>
       </c>
       <c r="E51">
-        <v>-22.25692652142252</v>
+        <v>-21.89843893355331</v>
       </c>
       <c r="F51">
-        <v>0.3052259045598177</v>
+        <v>0.08247128300780823</v>
       </c>
       <c r="G51">
-        <v>-8.326076150663997</v>
+        <v>-6.989459941910952</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.112292338904373</v>
       </c>
       <c r="E52">
-        <v>-21.83416630196244</v>
+        <v>-22.41751073820852</v>
       </c>
       <c r="F52">
-        <v>-0.1446786559834554</v>
+        <v>0.671571388447899</v>
       </c>
       <c r="G52">
-        <v>-7.987331199449152</v>
+        <v>-7.597166854918346</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.7452092781691328</v>
       </c>
       <c r="E53">
-        <v>-21.20011654225249</v>
+        <v>-21.60115367189777</v>
       </c>
       <c r="F53">
-        <v>-0.01341721407065134</v>
+        <v>0.06163784282740066</v>
       </c>
       <c r="G53">
-        <v>-8.018642339159578</v>
+        <v>-6.282946486738471</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.3886483421473457</v>
       </c>
       <c r="E54">
-        <v>-20.9412961388181</v>
+        <v>-20.8868638812459</v>
       </c>
       <c r="F54">
-        <v>0.1177042337510796</v>
+        <v>0.556328087003029</v>
       </c>
       <c r="G54">
-        <v>-8.472187078039731</v>
+        <v>-7.617980254723745</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.05179666068495126</v>
       </c>
       <c r="E55">
-        <v>-20.49260134871609</v>
+        <v>-19.81798099037142</v>
       </c>
       <c r="F55">
-        <v>-0.123513868841928</v>
+        <v>0.4346384304295732</v>
       </c>
       <c r="G55">
-        <v>-8.359919857711967</v>
+        <v>-8.026872355370207</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.255514746977104</v>
       </c>
       <c r="E56">
-        <v>-19.33156401178552</v>
+        <v>-21.2645340850116</v>
       </c>
       <c r="F56">
-        <v>-0.1067659366921276</v>
+        <v>0.09289545840463721</v>
       </c>
       <c r="G56">
-        <v>-8.868072045262398</v>
+        <v>-7.865698445790789</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.5203482774919048</v>
       </c>
       <c r="E57">
-        <v>-19.43806466349792</v>
+        <v>-19.36641514774855</v>
       </c>
       <c r="F57">
-        <v>0.1969856211382147</v>
+        <v>0.3908459593131746</v>
       </c>
       <c r="G57">
-        <v>-8.517349540286469</v>
+        <v>-8.276116707930857</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.735138364088178</v>
       </c>
       <c r="E58">
-        <v>-18.81500551020457</v>
+        <v>-19.76120751173725</v>
       </c>
       <c r="F58">
-        <v>-0.1459468864771414</v>
+        <v>0.2714740747327518</v>
       </c>
       <c r="G58">
-        <v>-8.409756810260156</v>
+        <v>-7.342311127668633</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8953418826229103</v>
       </c>
       <c r="E59">
-        <v>-18.71337296805043</v>
+        <v>-19.38573814633928</v>
       </c>
       <c r="F59">
-        <v>0.00949708502558858</v>
+        <v>0.4181240978873623</v>
       </c>
       <c r="G59">
-        <v>-8.978147684443165</v>
+        <v>-7.782487883661208</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9968676397836821</v>
       </c>
       <c r="E60">
-        <v>-18.79122196471629</v>
+        <v>-18.14286222714209</v>
       </c>
       <c r="F60">
-        <v>0.1202572620865077</v>
+        <v>0.06095692482229947</v>
       </c>
       <c r="G60">
-        <v>-9.273431793818459</v>
+        <v>-8.678387717498776</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.04131413308643</v>
       </c>
       <c r="E61">
-        <v>-17.57601049323195</v>
+        <v>-17.84279195397183</v>
       </c>
       <c r="F61">
-        <v>-0.3021935459931842</v>
+        <v>0.180986533120545</v>
       </c>
       <c r="G61">
-        <v>-8.857859012273746</v>
+        <v>-8.485290217284167</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.033614872610338</v>
       </c>
       <c r="E62">
-        <v>-16.54235913013715</v>
+        <v>-17.37433490330035</v>
       </c>
       <c r="F62">
-        <v>-0.3173808339561103</v>
+        <v>0.1539974947699344</v>
       </c>
       <c r="G62">
-        <v>-8.665436863349148</v>
+        <v>-8.411676926672932</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.9791874000670917</v>
       </c>
       <c r="E63">
-        <v>-17.53948835036009</v>
+        <v>-16.85271356777883</v>
       </c>
       <c r="F63">
-        <v>-0.2973823881177247</v>
+        <v>-0.2699253221845322</v>
       </c>
       <c r="G63">
-        <v>-9.224174186739642</v>
+        <v>-8.894579583395343</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.8864061434156487</v>
       </c>
       <c r="E64">
-        <v>-17.02532088305519</v>
+        <v>-17.17538998319538</v>
       </c>
       <c r="F64">
-        <v>-0.4474817331375923</v>
+        <v>-0.2606956525825402</v>
       </c>
       <c r="G64">
-        <v>-9.222992321982122</v>
+        <v>-8.694463726637478</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.7636432786999015</v>
       </c>
       <c r="E65">
-        <v>-16.42953220023604</v>
+        <v>-16.66782503099367</v>
       </c>
       <c r="F65">
-        <v>-0.7409507663969843</v>
+        <v>-0.07493509087215383</v>
       </c>
       <c r="G65">
-        <v>-9.10881160633266</v>
+        <v>-8.097651818999825</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.6188895565026793</v>
       </c>
       <c r="E66">
-        <v>-16.33209755348701</v>
+        <v>-17.06437897137135</v>
       </c>
       <c r="F66">
-        <v>-0.7268204752400304</v>
+        <v>-0.3902904192809116</v>
       </c>
       <c r="G66">
-        <v>-9.5644121939927</v>
+        <v>-9.066141984876992</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.4598897092250359</v>
       </c>
       <c r="E67">
-        <v>-16.66827334992042</v>
+        <v>-16.00659537028967</v>
       </c>
       <c r="F67">
-        <v>-0.8572717738328965</v>
+        <v>-0.5283916908386312</v>
       </c>
       <c r="G67">
-        <v>-9.431761944779643</v>
+        <v>-9.83463216309017</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.2922368256259771</v>
       </c>
       <c r="E68">
-        <v>-16.4101412745352</v>
+        <v>-16.65782616038473</v>
       </c>
       <c r="F68">
-        <v>-0.8203158188918022</v>
+        <v>-0.8100200404424072</v>
       </c>
       <c r="G68">
-        <v>-9.157178676661411</v>
+        <v>-8.494930525894524</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.1209525850958868</v>
       </c>
       <c r="E69">
-        <v>-16.10567385310349</v>
+        <v>-16.3329217357564</v>
       </c>
       <c r="F69">
-        <v>-1.056202548880392</v>
+        <v>-0.390668983183991</v>
       </c>
       <c r="G69">
-        <v>-8.949408838616751</v>
+        <v>-7.961830067160146</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.05028456098320958</v>
       </c>
       <c r="E70">
-        <v>-16.70937378001404</v>
+        <v>-16.5801718881012</v>
       </c>
       <c r="F70">
-        <v>-1.246066014336844</v>
+        <v>-0.9402220004470306</v>
       </c>
       <c r="G70">
-        <v>-9.103501491287668</v>
+        <v>-8.576651342531434</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.2209389131331083</v>
       </c>
       <c r="E71">
-        <v>-15.86453714066905</v>
+        <v>-15.79905087804413</v>
       </c>
       <c r="F71">
-        <v>-1.31810995572572</v>
+        <v>-1.009577061246419</v>
       </c>
       <c r="G71">
-        <v>-8.633715215991851</v>
+        <v>-9.013719496262635</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.3888665636491243</v>
       </c>
       <c r="E72">
-        <v>-16.04121555407831</v>
+        <v>-15.37253202515769</v>
       </c>
       <c r="F72">
-        <v>-1.54114870729689</v>
+        <v>-0.8509629276931755</v>
       </c>
       <c r="G72">
-        <v>-8.561565186508975</v>
+        <v>-8.790800601830268</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.5530037460685483</v>
       </c>
       <c r="E73">
-        <v>-15.49679788040217</v>
+        <v>-16.32337118407423</v>
       </c>
       <c r="F73">
-        <v>-1.543478904800965</v>
+        <v>-0.8697171656925563</v>
       </c>
       <c r="G73">
-        <v>-8.4574319765712</v>
+        <v>-8.351014490211327</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.7143732779258134</v>
       </c>
       <c r="E74">
-        <v>-16.13830150832876</v>
+        <v>-16.4407854581451</v>
       </c>
       <c r="F74">
-        <v>-1.718979307860277</v>
+        <v>-1.130642128798164</v>
       </c>
       <c r="G74">
-        <v>-7.992419507943012</v>
+        <v>-7.898933012459532</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.8715689002931853</v>
       </c>
       <c r="E75">
-        <v>-16.52539546650442</v>
+        <v>-15.85466959580634</v>
       </c>
       <c r="F75">
-        <v>-1.759324113846224</v>
+        <v>-1.245391723270966</v>
       </c>
       <c r="G75">
-        <v>-8.292447629076081</v>
+        <v>-6.815427873457005</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.022580950774694</v>
       </c>
       <c r="E76">
-        <v>-17.35906036047248</v>
+        <v>-16.49446598903203</v>
       </c>
       <c r="F76">
-        <v>-1.882948008305216</v>
+        <v>-1.580761236498762</v>
       </c>
       <c r="G76">
-        <v>-7.96380977339263</v>
+        <v>-7.048126119412377</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.166884302473805</v>
       </c>
       <c r="E77">
-        <v>-17.42192010817296</v>
+        <v>-15.89495037210456</v>
       </c>
       <c r="F77">
-        <v>-1.809170293942281</v>
+        <v>-1.370828085607284</v>
       </c>
       <c r="G77">
-        <v>-7.858901895798666</v>
+        <v>-8.224111348054445</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.301704752095931</v>
       </c>
       <c r="E78">
-        <v>-16.24571691179069</v>
+        <v>-17.23536056447896</v>
       </c>
       <c r="F78">
-        <v>-2.059105306714948</v>
+        <v>-1.142131584674993</v>
       </c>
       <c r="G78">
-        <v>-7.546578408532743</v>
+        <v>-7.42962676626691</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.423723331099459</v>
       </c>
       <c r="E79">
-        <v>-17.2898154644212</v>
+        <v>-18.19089122246744</v>
       </c>
       <c r="F79">
-        <v>-1.892501569561703</v>
+        <v>-1.520380708141304</v>
       </c>
       <c r="G79">
-        <v>-7.875335443855608</v>
+        <v>-7.023979000248933</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.530934707891489</v>
       </c>
       <c r="E80">
-        <v>-18.36398308446263</v>
+        <v>-18.50573790632473</v>
       </c>
       <c r="F80">
-        <v>-1.974454441822867</v>
+        <v>-1.631728197690808</v>
       </c>
       <c r="G80">
-        <v>-7.519815958393275</v>
+        <v>-6.657544646143623</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.619995882162499</v>
       </c>
       <c r="E81">
-        <v>-18.84510627693356</v>
+        <v>-18.55134416805598</v>
       </c>
       <c r="F81">
-        <v>-1.946849926491976</v>
+        <v>-1.211622497728441</v>
       </c>
       <c r="G81">
-        <v>-7.10779870275774</v>
+        <v>-6.652933056207418</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.687179932075757</v>
       </c>
       <c r="E82">
-        <v>-19.265724528188</v>
+        <v>-18.22279432185148</v>
       </c>
       <c r="F82">
-        <v>-1.865794176128044</v>
+        <v>-1.657376109216286</v>
       </c>
       <c r="G82">
-        <v>-7.243726392054676</v>
+        <v>-6.677970712120926</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.729933981805151</v>
       </c>
       <c r="E83">
-        <v>-20.10091551789666</v>
+        <v>-20.13751011635264</v>
       </c>
       <c r="F83">
-        <v>-2.170240734209335</v>
+        <v>-1.386605999528406</v>
       </c>
       <c r="G83">
-        <v>-6.831096685494376</v>
+        <v>-5.944396857710442</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.745648746907038</v>
       </c>
       <c r="E84">
-        <v>-20.63781139624605</v>
+        <v>-21.15842288206387</v>
       </c>
       <c r="F84">
-        <v>-2.258859478960826</v>
+        <v>-1.959456021627779</v>
       </c>
       <c r="G84">
-        <v>-6.463205691351787</v>
+        <v>-6.270641188968999</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.731942656313755</v>
       </c>
       <c r="E85">
-        <v>-20.97941230454066</v>
+        <v>-21.28373934327813</v>
       </c>
       <c r="F85">
-        <v>-2.224179877642625</v>
+        <v>-1.334545593364665</v>
       </c>
       <c r="G85">
-        <v>-6.384666308978117</v>
+        <v>-5.842806146746827</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.686413835673734</v>
       </c>
       <c r="E86">
-        <v>-22.44146636570909</v>
+        <v>-23.32649774034617</v>
       </c>
       <c r="F86">
-        <v>-2.246662597322007</v>
+        <v>-1.823774411253636</v>
       </c>
       <c r="G86">
-        <v>-6.745376729846027</v>
+        <v>-6.189221631976164</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.607461038989536</v>
       </c>
       <c r="E87">
-        <v>-23.86100711289352</v>
+        <v>-22.75243214734181</v>
       </c>
       <c r="F87">
-        <v>-2.482199756266615</v>
+        <v>-1.776259257029057</v>
       </c>
       <c r="G87">
-        <v>-6.157013334424595</v>
+        <v>-5.915297162420248</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.494769814061703</v>
       </c>
       <c r="E88">
-        <v>-25.12573744765173</v>
+        <v>-25.20913382497699</v>
       </c>
       <c r="F88">
-        <v>-2.405296611692918</v>
+        <v>-1.78963490548206</v>
       </c>
       <c r="G88">
-        <v>-6.316346580684177</v>
+        <v>-5.705147042132852</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.346703055632781</v>
       </c>
       <c r="E89">
-        <v>-25.71550778851469</v>
+        <v>-25.93262094633843</v>
       </c>
       <c r="F89">
-        <v>-2.447591394545054</v>
+        <v>-1.633295468816904</v>
       </c>
       <c r="G89">
-        <v>-5.790943140328604</v>
+        <v>-5.894490383705929</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.163437102574318</v>
       </c>
       <c r="E90">
-        <v>-27.21401606544487</v>
+        <v>-27.07765012765189</v>
       </c>
       <c r="F90">
-        <v>-2.136929595840559</v>
+        <v>-1.872141127168294</v>
       </c>
       <c r="G90">
-        <v>-6.154772095094508</v>
+        <v>-6.077199392018305</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.9479852453064207</v>
       </c>
       <c r="E91">
-        <v>-29.12153611474784</v>
+        <v>-29.25616311852187</v>
       </c>
       <c r="F91">
-        <v>-2.568203345127468</v>
+        <v>-1.903737545013276</v>
       </c>
       <c r="G91">
-        <v>-6.192409687330482</v>
+        <v>-5.973198603902101</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.7013133996952019</v>
       </c>
       <c r="E92">
-        <v>-30.17238209364977</v>
+        <v>-30.83314532153097</v>
       </c>
       <c r="F92">
-        <v>-2.471990956394514</v>
+        <v>-2.391688191999727</v>
       </c>
       <c r="G92">
-        <v>-6.068396651429383</v>
+        <v>-5.609452412774679</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.4271613167272945</v>
       </c>
       <c r="E93">
-        <v>-31.44717243341601</v>
+        <v>-32.08617634369036</v>
       </c>
       <c r="F93">
-        <v>-2.489221826740147</v>
+        <v>-1.981996727025356</v>
       </c>
       <c r="G93">
-        <v>-7.04747394194114</v>
+        <v>-6.237601944487073</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1335803696800855</v>
       </c>
       <c r="E94">
-        <v>-33.5687760914316</v>
+        <v>-33.77280422361019</v>
       </c>
       <c r="F94">
-        <v>-2.372129609252228</v>
+        <v>-2.244635582287356</v>
       </c>
       <c r="G94">
-        <v>-6.767842091875521</v>
+        <v>-6.024823251041496</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.174464500112738</v>
       </c>
       <c r="E95">
-        <v>-34.65830655954405</v>
+        <v>-35.09096375894789</v>
       </c>
       <c r="F95">
-        <v>-2.812023349732669</v>
+        <v>-1.772788397611327</v>
       </c>
       <c r="G95">
-        <v>-6.805194977195118</v>
+        <v>-6.52160702521007</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.4901682955694391</v>
       </c>
       <c r="E96">
-        <v>-37.10543051465301</v>
+        <v>-38.39082201207121</v>
       </c>
       <c r="F96">
-        <v>-2.744087282294276</v>
+        <v>-2.544724099462519</v>
       </c>
       <c r="G96">
-        <v>-6.640991918447267</v>
+        <v>-6.108487357909957</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8019829628038101</v>
       </c>
       <c r="E97">
-        <v>-38.62698193157122</v>
+        <v>-39.25876519004034</v>
       </c>
       <c r="F97">
-        <v>-2.679622902641016</v>
+        <v>-2.189679203683429</v>
       </c>
       <c r="G97">
-        <v>-8.062904333019635</v>
+        <v>-6.791641603757342</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.104471544018488</v>
       </c>
       <c r="E98">
-        <v>-40.71187777928063</v>
+        <v>-41.43794160235244</v>
       </c>
       <c r="F98">
-        <v>-2.841269689255908</v>
+        <v>-2.005892641493913</v>
       </c>
       <c r="G98">
-        <v>-7.808184338137031</v>
+        <v>-7.159251201529093</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.388498115964519</v>
       </c>
       <c r="E99">
-        <v>-43.34148791571368</v>
+        <v>-42.80221458851025</v>
       </c>
       <c r="F99">
-        <v>-2.680047026751249</v>
+        <v>-2.532012801666561</v>
       </c>
       <c r="G99">
-        <v>-7.899270688104538</v>
+        <v>-7.146737339390648</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.646762078955369</v>
       </c>
       <c r="E100">
-        <v>-44.77097998452997</v>
+        <v>-45.85912247535907</v>
       </c>
       <c r="F100">
-        <v>-2.976658057569459</v>
+        <v>-2.426197149632952</v>
       </c>
       <c r="G100">
-        <v>-7.871405826300493</v>
+        <v>-7.048543248150325</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.869174930871194</v>
       </c>
       <c r="E101">
-        <v>-47.28916701800429</v>
+        <v>-47.79154686746722</v>
       </c>
       <c r="F101">
-        <v>-2.907385833510351</v>
+        <v>-2.367758314467655</v>
       </c>
       <c r="G101">
-        <v>-8.717273385403056</v>
+        <v>-8.308553433124635</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.057322520602335</v>
       </c>
       <c r="E102">
-        <v>-49.29942795347478</v>
+        <v>-49.50830268496007</v>
       </c>
       <c r="F102">
-        <v>-2.905444968685592</v>
+        <v>-2.228695308355285</v>
       </c>
       <c r="G102">
-        <v>-8.735239716044681</v>
+        <v>-7.786397637943088</v>
       </c>
     </row>
   </sheetData>
